--- a/docs/Bug_Report/Bug_Report.xlsx
+++ b/docs/Bug_Report/Bug_Report.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\NAM4\NAM4-KY2\CNMoi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TESTING\SecureStudy-Testing\docs\Bug_Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE2BC2A-C8D6-4D9C-8828-E333904D5777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21096" windowHeight="6912"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="119">
   <si>
     <t>Bug ID</t>
   </si>
@@ -50,9 +51,6 @@
     <t>Priority</t>
   </si>
   <si>
-    <t>BUG-TC_LOGIN_APP_01</t>
-  </si>
-  <si>
     <t>Đăng nhập qua ứng dụng với user không tồn tại không hiển thị thông báo lỗi cụ thể</t>
   </si>
   <si>
@@ -71,9 +69,6 @@
     <t>P1 (Medium)</t>
   </si>
   <si>
-    <t>BUG-TC_LOGIN_APP_03</t>
-  </si>
-  <si>
     <t>Đăng nhập qua ứng dụng với user admin bị chặn vẫn cho phép truy cập</t>
   </si>
   <si>
@@ -89,33 +84,15 @@
     <t>Critical</t>
   </si>
   <si>
-    <t>BUG-TC_ROLE_APP_01</t>
-  </si>
-  <si>
-    <t>Phân quyền truy cập TaskPanel không đúng với vai trò customer</t>
-  </si>
-  <si>
     <t>Email 1: camtu18@gmail.com Email 2: tuchuc848@gmail.com</t>
   </si>
   <si>
-    <t>Với camtu18@gmail.com, giao diện chuyển sang TaskPanel. Với tuchuc848@gmail.com, hiển thị thông báo lỗi và yêu cầu chuyển hướng đến web.</t>
-  </si>
-  <si>
     <t>Với testuser15@gmail.com, giao diện chuyển sang TaskPanel. Với testuser16@gmail.com, giao diện vẫn chuyển sang TaskPanel (không đúng).</t>
   </si>
   <si>
-    <t>BUG-TC_ROLE_APP_02</t>
-  </si>
-  <si>
     <t>Phân quyền truy cập TaskPanel gây lỗi NullPointerException</t>
   </si>
   <si>
-    <t>Với testuser15@gmail.com, lỗi NullPointerException xuất hiện trong log. Với testuser16@gmail.com, lỗi NullPointerException xuất hiện, không hiển thị thông báo.</t>
-  </si>
-  <si>
-    <t>BUG-TC_GETUSER_APP_01</t>
-  </si>
-  <si>
     <t>Table không hiển thị danh sách người dùng và nút Refresh không hoạt động</t>
   </si>
   <si>
@@ -128,57 +105,30 @@
     <t>Table không hiển thị danh sách về thông tin người dùng như trong cơ sở dữ liệu. Nhấn nút Refresh cũng không load được thông tin người dùng.</t>
   </si>
   <si>
-    <t>BUG-TC_GETUSER_APP_02</t>
-  </si>
-  <si>
     <t>Hiển thị danh sách người dùng nhưng một số trường bị thiếu (null)</t>
   </si>
   <si>
     <t>Có hiển thị thông tin người dùng, nhưng một số trường bị thiếu (null). Nhấn nút Refresh thông tin người dùng không bị biến mất.</t>
   </si>
   <si>
-    <t>BUG-TC_ADDUSER_APP_01</t>
-  </si>
-  <si>
     <t>Thêm người dùng mới không thành công</t>
   </si>
   <si>
-    <t>email: testuser21@gmail.com họ tên: Cam Tu Nguyen sdt: 0909090</t>
-  </si>
-  <si>
     <t>Người dùng mới xuất hiện trong Table. Bảng account chứa bản ghi mới.</t>
   </si>
   <si>
     <t>Thông báo lỗi: “Lỗi khi thêm người dùng!” Người dùng mới không xuất hiện trong JTable. Bảng account không có bản ghi mới.</t>
   </si>
   <si>
-    <t>BUG-TC_ADDUSER_APP_02</t>
-  </si>
-  <si>
-    <t>Thêm người dùng mới gây lỗi 404 Not Found</t>
-  </si>
-  <si>
-    <t>Thông báo lỗi: “Lỗi khi thêm người dùng!” Người dùng mới không xuất hiện trong JTable. Bảng account không có bản ghi mới. Log: "404 Not Found - Endpoint /create not defined".</t>
-  </si>
-  <si>
-    <t>BUG-TC_ADDUSER_APP_04</t>
-  </si>
-  <si>
     <t>Thêm người dùng với email đã tồn tại cho phép thêm vào cơ sở dữ liệu</t>
   </si>
   <si>
-    <t>email: testuser22@gmail.com họ tên: Cam Tu Nguyen sdt: 0909090</t>
-  </si>
-  <si>
     <t>Thông báo lỗi: “Email này đã được sử dụng cho tài khoản khác. Vui lòng chọn email khác!” Trong Table và Database không cập nhật thêm user mới.</t>
   </si>
   <si>
     <t>Thông báo: “Thêm người dùng thành công!” Người dùng mới được cập nhật vào Table và Database. Trong cơ sở dữ liệu tồn tại 2 tài khoản có email giống nhau.</t>
   </si>
   <si>
-    <t>BUG-TC_DELETEUSER_APP_01</t>
-  </si>
-  <si>
     <t>Xóa người dùng không thành công</t>
   </si>
   <si>
@@ -188,18 +138,6 @@
     <t>Tài khoản và tất cả thông tin của testuser21@gmail.com bị xóa khỏi Table và database.</t>
   </si>
   <si>
-    <t>Thông báo lỗi: “Lỗi khi xóa người dùng!” Tài khoản và tất cả thông tin của testuser21@gmail.com không bị xóa. Bảng account vẫn còn hiển thị người dùng testuser21@gmail.com.</t>
-  </si>
-  <si>
-    <t>BUG-TC_DELETEUSER_APP_02</t>
-  </si>
-  <si>
-    <t>Thông báo lỗi: “Lỗi khi xóa người dùng!” Tài khoản và tất cả thông tin của testuser21@gmail.com không bị xóa. Bảng account vẫn còn ghi của testuser21@gmail.com.</t>
-  </si>
-  <si>
-    <t>BUG-TC_UPDATEUSER_APP_01</t>
-  </si>
-  <si>
     <t>Sửa thông tin người dùng không hiển thị dữ liệu trong EditUserDialog</t>
   </si>
   <si>
@@ -212,55 +150,10 @@
     <t>EditUserDialog mở nhưng các trường trống (email, role, status không được điền). Nhấn "Save" không có tác dụng, Table và database không thay đổi. Log: "No data retrieved for selected row, invalid row selection in JTable".</t>
   </si>
   <si>
-    <t>BUG-TC_UPDATEUSER_APP_02</t>
-  </si>
-  <si>
     <t>Sửa thông tin người dùng gây lỗi 500 Internal Server Error</t>
   </si>
   <si>
     <t>EditUserDialog hiển thị đúng thông tin: email: "testuser21@gmail.com", role: "customer", status: "Active", phone: “7878”. Sau khi nhấn "Save", giao diện không cập nhật. Log: "500 Internal Server Error - Endpoint /update failed to process PUT request". Database không thay đổi.</t>
-  </si>
-  <si>
-    <t>BUG-TC_LOGOUT_APP_01</t>
-  </si>
-  <si>
-    <t>Đăng xuất làm ứng dụng đóng hoàn toàn</t>
-  </si>
-  <si>
-    <t>Giao diện chuyển về LoginPanel. Token bị xóa khỏi Preferences và user_tokens.</t>
-  </si>
-  <si>
-    <t>Ứng dụng đóng hoàn toàn, không chuyển về LoginPanel. Token không bị xóa khỏi Preferences và user_tokens.</t>
-  </si>
-  <si>
-    <t>BUG-TC_LOGOUT_APP_02</t>
-  </si>
-  <si>
-    <t>Đăng xuất không xóa token khỏi Preferences và user_tokens</t>
-  </si>
-  <si>
-    <t>Giao diện chuyển về LoginPanel. Token vẫn tồn tại trong Preferences và user_tokens.</t>
-  </si>
-  <si>
-    <t>1. Chạy ứng dụng Java và đăng nhập với email không tồn tại trong cơ sở dữ liệu. 
-2. Nhấn nút "Login with Google". 
-3. Kiểm tra response và giao diện.</t>
-  </si>
-  <si>
-    <t>1. Chạy ứng dụng Java và đăng nhập với email camtu7092003@gmail.com (role: admin, status: Blocked). 
-2. Nhấn nút "Login with Google". 
-3. Kiểm tra response và giao diện.</t>
-  </si>
-  <si>
-    <t>1. Đăng nhập với camtu7092003@gmail.com (role: admin, status: Active) trên ứng dụng. 
-2. Kiểm tra giao diện. 
-3. Đăng xuất, sau đó đăng nhập với tuchuc848@gmail.com (role: customer, status: Active). 
-4. Kiểm tra giao diện.</t>
-  </si>
-  <si>
-    <t>1. Đăng nhập với testuser15@gmail.com (role: admin). 
-2. Kiểm tra Table hiển thị danh sách công việc. 
-3. Nhấn nút Refresh giao diện.</t>
   </si>
   <si>
     <t>1. Đăng nhập với testuser15@gmail.com (role: admin). 
@@ -292,16 +185,269 @@
 6. Kiểm tra giao diện và database.</t>
   </si>
   <si>
+    <t>BUG_LOGIN_APP_01</t>
+  </si>
+  <si>
+    <t>BUG_LOGIN_APP_02</t>
+  </si>
+  <si>
+    <t>BUG_ROLE_APP_01</t>
+  </si>
+  <si>
+    <t>BUG_ROLE_APP_02</t>
+  </si>
+  <si>
+    <t>BUG_GETUSER_APP_01</t>
+  </si>
+  <si>
+    <t>BUG_GETUSER_APP_02</t>
+  </si>
+  <si>
+    <t>BUG_ADDUSER_APP_01</t>
+  </si>
+  <si>
+    <t>BUG_ADDUSER_APP_02</t>
+  </si>
+  <si>
+    <t>BUG_DELETEUSER_APP_01</t>
+  </si>
+  <si>
+    <t>BUG_ADDUSER_APP_03</t>
+  </si>
+  <si>
+    <t>BUG_UPDATEUSER_APP_01</t>
+  </si>
+  <si>
+    <t>BUG_UPDATEUSER_APP_02</t>
+  </si>
+  <si>
+    <t>1. Chạy ứng dụng Java và đăng nhập với email không tồn tại trong cơ sở dữ liệu. 
+2. Nhấn nút "Đăng nhập bằng Google". 
+3. Kiểm tra response và giao diện.</t>
+  </si>
+  <si>
+    <t>1. Chạy ứng dụng Java và đăng nhập với email camtu7092003@gmail.com (role: admin, status: Blocked). 
+2. Nhấn nút "Đăng nhập bằng Google". 
+3. Kiểm tra response và giao diện.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập với camtu7092003@gmail.com (role: admin, status: Active) trên ứng dụng. 
+2. Kiểm tra giao diện. 
+3. Đăng xuất, sau đó đăng nhập với tuchuc848@gmail.com (role: student, status: Active). 
+4. Kiểm tra giao diện.</t>
+  </si>
+  <si>
+    <t>Với camtu18@gmail.com, giao diện chuyển sang TaskPanel. Với tuchuc848@gmail.com, chuyển hướng vào StudentDashoboard.</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập với camtu7092003@gmail.com (role: admin, status: Active) trên ứng dụng. 
+2. Kiểm tra giao diện. 
+3. Đăng xuất, sau đó đăng nhập với tuchuc848@gmail.com (role: teacher, status: Active). 
+4. Kiểm tra giao diện.</t>
+  </si>
+  <si>
+    <t>Với camtu18@gmail.com, giao diện chuyển sang TaskPanel. Với tuchuc848@gmail.com, chuyển hướng vào TeacherDashoboard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cả hai tài khoản khi đăng nhập bị xuất hiện lỗi NullPointerException trong log. </t>
+  </si>
+  <si>
     <t>1. Đăng nhập với testuser15@gmail.com (role: admin). 
-2. Nhấn nút "Logout" trên TaskPanel. 
-3. Kiểm tra giao diện và bảng user_tokens.</t>
+2. Kiểm tra Table hiển thị danh sách người dùng. 
+3. Nhấn nút Refresh giao diện.</t>
+  </si>
+  <si>
+    <t>email: testuser21@gmail.com họ tên: Cam Tu Nguyen 
+role: teacher
+sdt: 0909090</t>
+  </si>
+  <si>
+    <t>email: testuser21@gmail.com họ tên: Cam Tu Nguyen 
+role: teacher
+sdt: 0909091</t>
+  </si>
+  <si>
+    <t>Thêm người dùng mới nhưng dữ liệu không được cập nhật dữ liệu đây đủ trong DB</t>
+  </si>
+  <si>
+    <t>Người dùng mới xuất hiện trong Table. Bảng account chứa bản ghi mới, các bảng liên quan cũng có bản ghi mới (admin/teacher/student).</t>
+  </si>
+  <si>
+    <t>Thông báo: "Thêm người dùng thành công!". Bảng account có bảng ghi mới, nhưng các bảng liên quan không có bảng ghi mới tương ứng với người dùng vừa được thêm</t>
+  </si>
+  <si>
+    <t>email: testuser22@gmail.com họ tên: Cam Tu Nguyen 
+role: student
+sdt: 0909090</t>
+  </si>
+  <si>
+    <t>Thông báo lỗi: “Lỗi khi xóa người dùng!” Tài khoản và tất cả thông tin của testuser21@gmail.com không bị xóa. Bảng account và các bảng liên quan vẫn còn hiển thị người dùng testuser21@gmail.com.</t>
+  </si>
+  <si>
+    <t>BUG_LKT_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Đăng nhập với testuser16@gmail.com (role: student). 
+2. Chọn lớp bất kỳ
+3. Chọn nút "Làm kiểm tra" của bài kiểm tra bất kỳ 
+4. Quan sát số câu trong giao diện làm bài kiểm tra
+</t>
+  </si>
+  <si>
+    <t>Số câu hiển thị phải bằng với số câu yêu cầu của đề (ví dụ: 10 câu)</t>
+  </si>
+  <si>
+    <t>Số câu hiển thị không đúng với số câu yêu cầu của đề (ví dụ 5 câu thay vì 10 câu)</t>
+  </si>
+  <si>
+    <t>BUG_LKT_02</t>
+  </si>
+  <si>
+    <t>Giao diện kiểm tra không hiển thị đúng số câu yêu cầu của đề kiểm tra</t>
+  </si>
+  <si>
+    <t>Một số câu hỏi trong bài kiểm tra không thuộc lớp của bài kiểm tra đang làm</t>
+  </si>
+  <si>
+    <t>Giao diện kiểm tra hiển thị đúng số lượng câu hỏi nhưng một số câu hỏi trong bài kiểm tra không thuộc lớp của bài kiểm tra đang làm (bài kiểm tra thuộc lớp A nhưng có một số câu hỏi thuộc lớp B và lớp C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giao diện kiểm tra hiển thị các câu hỏi thuộc về lớp của bài kiểm tra </t>
+  </si>
+  <si>
+    <t>BUG_LKT_03</t>
+  </si>
+  <si>
+    <t>Bài làm kiểm tra không tự khôi phục khi truy cập lại sau khi gặp sự cố</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Các câu hỏi và lựa chọn phải được giữ nguyên khi truy cập lại bài kiểm tra sau khi gặp sự cố </t>
+  </si>
+  <si>
+    <t>Giao diện hiển thị các câu hỏi khác với các câu ban đầu, chức năng recovery chưa hoạt động</t>
+  </si>
+  <si>
+    <t>BUG_LKT_04</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập với testuser16@gmail.com (role: student). 
+2. Chọn lớp bất kỳ
+3. Chọn nút "Làm kiểm tra" của bài kiểm tra bất kỳ 
+4. Chọn đáp án cho một số câu hỏi
+5. Bấm "Nộp bài"
+6. Kiểm tra dữ liệu trong DB</t>
+  </si>
+  <si>
+    <t>Status bài kiểm tra tại bảng exam_attempts được cập nhật thành "submitted"</t>
+  </si>
+  <si>
+    <t>Status bài kiểm tra tại bảng exam_attempts vẫn là "in_progress"</t>
+  </si>
+  <si>
+    <t>BUG_TKT_01</t>
+  </si>
+  <si>
+    <t>Dữ liệu bài kiểm tra đã làm được lưu vào DB nhưng không cập nhật status bài kiểm tra</t>
+  </si>
+  <si>
+    <t>Tạo bài kiểm tra thành công nhưng dữ liệu không lưu vào DB</t>
+  </si>
+  <si>
+    <t>Thông báo: "Tạo bài kiểm tra thành công!"
+Dữ liệu bài kiểm tra được lưu vào bảng "exams"</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập với testuser17@gmail.com (role: teacher). 
+2. Chọn lớp bất kỳ
+3. Chọn nút "Tạo bài kiểm tra" 
+4. Nhập các thông tin cần thiết cho bài kiểm tra
+5. Bấm "Tạo Bài Kiểm Tra"
+6. Kiểm tra dữ liệu trong bảng "exams"</t>
+  </si>
+  <si>
+    <t>Thông báo: "Tạo bài kiểm tra thành công!"
+Dữ liệu bài kiểm tra không xuất hiện trong bảng "exams"</t>
+  </si>
+  <si>
+    <t>BUG_VerifyJWT</t>
+  </si>
+  <si>
+    <t>JWT giả mạo vẫn thao tác được trong hệ thống</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Đăng nhập vào hệ thống
+2. Dùng Thunder Client gửi request gồm thông tin của user vừa đăng nhập + JWT giả </t>
+  </si>
+  <si>
+    <t>Hệ thống từ chối truy cập và thông báo lỗi</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về kết quả 200, chức năng được cho phép thực hiện thành công</t>
+  </si>
+  <si>
+    <t>BUG_VerifyGGtoken</t>
+  </si>
+  <si>
+    <t>Google token giả mạo hoặc đã hết hạn, hệ thống vẫn cấp JWT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Dùng Thunder Client gửi request endpoint /appLogin với token google giả
+</t>
+  </si>
+  <si>
+    <t>Hệ thống hiển thị lỗi "Google access token không hợp lệ hoặc đã hết hạn"</t>
+  </si>
+  <si>
+    <t>Hệ thống trả về auth_token (JWT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phân quyền truy cập TaskPanel không đúng với vai trò </t>
+  </si>
+  <si>
+    <t>BUG_ROLE_01</t>
+  </si>
+  <si>
+    <t>Người dùng không có quyền admin vẫn xem được danh sách tất cả người dùng trong hệ thống</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập hệ thống (web/app)
+2. Dùng Thunder Client, viết request gồm thông tin người dùng vừa đăng nhập gồm auth_token và tên bảng muốn xem</t>
+  </si>
+  <si>
+    <t>{
+  "email": "camtunguyen.alexia@gmail.com",
+  "role": "student",
+  "table": "account"
+}</t>
+  </si>
+  <si>
+    <t>Người dùng có role là teacher và student chỉ xem được thông tin cá nhân của mình</t>
+  </si>
+  <si>
+    <t>Người dùng có role là teacher và student  xem được tất cả thông tin của tất cả người dùng trong hệ thống</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>P0 (High)</t>
+  </si>
+  <si>
+    <t>P2 (Minor)</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập với testuser16@gmail.com (role: student). 
+2. Chọn lớp bất kỳ
+3. Chọn nút "Làm kiểm tra" của bài kiểm tra bất kỳ 
+4. Chọn đáp án cho một số câu hỏi
+5. Tắt ứng dụng mà chưa nộp bài</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,6 +474,19 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -343,7 +502,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -431,11 +590,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -444,28 +627,42 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -745,456 +942,621 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="35" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="39.21875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" style="10" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="8"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="6.7265625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="22.54296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="35.7265625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="28.08984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="39.1796875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.6328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="13" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" s="9" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11"/>
-      <c r="J1" s="12"/>
-    </row>
-    <row r="2" spans="1:10" ht="63" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="17">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="108" x14ac:dyDescent="0.3">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="216" x14ac:dyDescent="0.3">
+      <c r="A4" s="17">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="162" x14ac:dyDescent="0.3">
+      <c r="A5" s="17">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="135" x14ac:dyDescent="0.3">
+      <c r="A6" s="17">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="81" x14ac:dyDescent="0.3">
+      <c r="A7" s="17">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="81" x14ac:dyDescent="0.3">
+      <c r="A8" s="17">
+        <v>7</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="94.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="17">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="94.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="17">
+        <v>9</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="H10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="176.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="17">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="B11" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="160" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="17">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="B12" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="I12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="3" t="s">
+    </row>
+    <row r="13" spans="1:10" ht="178.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="17">
+        <v>12</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="172.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="17">
+        <v>13</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="17">
         <v>14</v>
       </c>
-      <c r="I2" s="7"/>
-    </row>
-    <row r="3" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="B15" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="126.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="17">
         <v>15</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B16" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="148.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="17">
         <v>16</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="B17" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="162" x14ac:dyDescent="0.3">
+      <c r="A18" s="17">
         <v>17</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="B18" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="158.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="17">
         <v>18</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="B19" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="7"/>
+      <c r="F19" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="108" x14ac:dyDescent="0.3">
+      <c r="A20" s="17">
         <v>19</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="B20" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="17">
         <v>20</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="7"/>
-    </row>
-    <row r="4" spans="1:10" ht="113.4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" spans="1:10" ht="113.4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="7"/>
-    </row>
-    <row r="6" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="7"/>
-    </row>
-    <row r="7" spans="1:10" ht="75.599999999999994" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="8" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="7"/>
-    </row>
-    <row r="10" spans="1:10" ht="100.8" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="7"/>
-    </row>
-    <row r="11" spans="1:10" ht="126" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="7"/>
-    </row>
-    <row r="12" spans="1:10" ht="126" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" ht="138.6" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="7"/>
-    </row>
-    <row r="14" spans="1:10" ht="138.6" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="7"/>
-    </row>
-    <row r="15" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="7"/>
-    </row>
-    <row r="16" spans="1:10" ht="88.2" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="7"/>
+      <c r="B21" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" s="7"/>
+      <c r="F21" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>116</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>